--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488224_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488224_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. SOSA LLANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0794</v>
+        <v>4.0747</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1045</v>
+        <v>4.7834</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.0251</v>
+        <v>-0.7086</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.5799</v>
+        <v>3.6776</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8669</v>
+        <v>0.5258</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.4468</v>
+        <v>3.1518</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0086</v>
+        <v>4.959</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7906</v>
+        <v>0.3865</v>
       </c>
       <c r="L2" t="n">
-        <v>0.218</v>
+        <v>4.5725</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.5885</v>
+        <v>-1.2814</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9237</v>
+        <v>0.1393</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.6648</v>
+        <v>-1.4207</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9361</v>
+        <v>-0.6034</v>
       </c>
       <c r="T2" t="n">
-        <v>4.7815</v>
+        <v>-0.1756</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1547</v>
+        <v>-0.4278</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9444</v>
+        <v>0.63</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. SOSA LLANO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8728</v>
+        <v>0.9949</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6307</v>
+        <v>4.9708</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7579</v>
+        <v>-3.9759</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6776</v>
+        <v>-1.5799</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5258</v>
+        <v>0.8669</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1518</v>
+        <v>-2.4468</v>
       </c>
       <c r="J3" t="n">
-        <v>4.959</v>
+        <v>3.0086</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3865</v>
+        <v>2.7906</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5725</v>
+        <v>0.218</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2814</v>
+        <v>-4.5885</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1393</v>
+        <v>-1.9237</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4207</v>
+        <v>-2.6648</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8053</v>
+        <v>1.8517</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3283</v>
+        <v>1.6477</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.477</v>
+        <v>0.2039</v>
       </c>
       <c r="V3" t="n">
-        <v>0.63</v>
+        <v>-0.9444</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X3" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.5034</v>
+        <v>-0.9613</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0658</v>
+        <v>2.0019</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5693</v>
+        <v>-2.9632</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3613</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2713</v>
+        <v>0.2708</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6603</v>
+        <v>0.2758</v>
       </c>
       <c r="U4" t="n">
-        <v>0.389</v>
+        <v>-0.005</v>
       </c>
       <c r="V4" t="n">
         <v>0.3144</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2599</v>
+        <v>-1.7859</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9584</v>
+        <v>3.4661</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.2183</v>
+        <v>-5.252</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0607</v>
+        <v>-3.5719</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3783</v>
+        <v>-2.2185</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.439</v>
+        <v>-1.3534</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3003</v>
+        <v>2.6815</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0514</v>
+        <v>0.6482</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2488</v>
+        <v>2.0333</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.361</v>
+        <v>-6.2534</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6731</v>
+        <v>-2.8667</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.6878</v>
+        <v>-3.3867</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4308</v>
+        <v>0.4334</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9002</v>
+        <v>0.4707</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4693</v>
+        <v>-0.0373</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2594</v>
+        <v>-0.315</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3155</v>
+        <v>0.3139</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9439</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>M. JIMENEZ CUEVAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3488</v>
+        <v>-2.5077</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8785</v>
+        <v>-0.144</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.2274</v>
+        <v>-2.3637</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.5719</v>
+        <v>-1.9103</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2185</v>
+        <v>-1.4189</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3534</v>
+        <v>-0.4915</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6815</v>
+        <v>0.5752</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6482</v>
+        <v>-0.2234</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0333</v>
+        <v>0.7986</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.2534</v>
+        <v>-2.4855</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.8667</v>
+        <v>-1.1954</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.3867</v>
+        <v>-1.2901</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6676</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6676</v>
+        <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1296</v>
+        <v>-0.7085</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1169</v>
+        <v>-0.0892</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0127</v>
+        <v>-0.6193</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.315</v>
+        <v>-0.63</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3139</v>
+        <v>-0.63</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. JIMENEZ CUEVAS</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.0094</v>
+        <v>-3.1878</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5472</v>
+        <v>0.203</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4622</v>
+        <v>-3.3908</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9103</v>
+        <v>-1.4913</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4189</v>
+        <v>-0.9645</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4915</v>
+        <v>-0.5268</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5752</v>
+        <v>1.6467</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2234</v>
+        <v>0.1845</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7986</v>
+        <v>1.4622</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4855</v>
+        <v>-3.138</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1954</v>
+        <v>-1.149</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2901</v>
+        <v>-1.989</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7411</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2102</v>
+        <v>0.4887</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4924</v>
+        <v>0.4091</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7178</v>
+        <v>0.0796</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.63</v>
+        <v>-1.2589</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RUEDA MURIEL</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9528</v>
+        <v>-3.7917</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2791</v>
+        <v>0.5989</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.6737</v>
+        <v>-4.3907</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8657</v>
+        <v>-2.0607</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1341</v>
+        <v>0.3783</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.9997</v>
+        <v>-2.439</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.142</v>
+        <v>1.3003</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3865</v>
+        <v>1.0514</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5284</v>
+        <v>0.2488</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7237</v>
+        <v>-3.361</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2524</v>
+        <v>-0.6731</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.4713</v>
+        <v>-2.6878</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1602</v>
+        <v>-0.101</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1604</v>
+        <v>0.5406</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3206</v>
+        <v>-0.6417</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6289</v>
+        <v>-1.2594</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6289</v>
+        <v>-0.3155</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>M. RUEDA MURIEL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4724</v>
+        <v>-3.8735</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0816</v>
+        <v>-0.2244</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3908</v>
+        <v>-3.6491</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4913</v>
+        <v>-3.8657</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9645</v>
+        <v>0.1341</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5268</v>
+        <v>-3.9997</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6467</v>
+        <v>-0.142</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1845</v>
+        <v>0.3865</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4622</v>
+        <v>-0.5284</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.138</v>
+        <v>-3.7237</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.149</v>
+        <v>-0.2524</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.989</v>
+        <v>-3.4713</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.5558999999999999</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.8529</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.0808</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8754</v>
+        <v>0.2151</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0796</v>
+        <v>-0.296</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2589</v>
+        <v>0.6289</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.936199999999999</v>
+        <v>-7.656</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8575</v>
+        <v>-1.8235</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.0787</v>
+        <v>-5.8324</v>
       </c>
       <c r="G10" t="n">
         <v>-7.6212</v>
@@ -1234,13 +1234,13 @@
         <v>1.6676</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0943</v>
+        <v>0.1859</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.715</v>
+        <v>0.319</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3793</v>
+        <v>-0.1331</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8883</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.1244</v>
+        <v>-8.4137</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.759</v>
+        <v>-3.1715</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.3653</v>
+        <v>-5.2422</v>
       </c>
       <c r="G11" t="n">
         <v>-5.7876</v>
@@ -1312,13 +1312,13 @@
         <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7074</v>
+        <v>-0.9967</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9302</v>
+        <v>-0.3426</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7772</v>
+        <v>-0.6541</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-27.6551</v>
+        <v>-27.108</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1135</v>
+        <v>10.6607</v>
       </c>
       <c r="F12" t="n">
-        <v>-37.7687</v>
+        <v>-37.76859999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-25.5723</v>
@@ -1390,13 +1390,13 @@
         <v>11.1173</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1927000000000001</v>
+        <v>0.7400999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.723600000000001</v>
+        <v>3.2706</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.5306</v>
+        <v>-2.5308</v>
       </c>
       <c r="V12" t="n">
         <v>-5.981599999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.7625</v>
+        <v>8.2516</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7102</v>
+        <v>7.2978</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0522</v>
+        <v>0.9537</v>
       </c>
       <c r="G13" t="n">
         <v>8.7819</v>
@@ -1468,13 +1468,13 @@
         <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.4197</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6354</v>
+        <v>-0.0479</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2734</v>
+        <v>-0.3719</v>
       </c>
       <c r="V13" t="n">
         <v>0.6304999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3206</v>
+        <v>7.9344</v>
       </c>
       <c r="E14" t="n">
-        <v>8.611599999999999</v>
+        <v>8.9054</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.291</v>
+        <v>-0.9709</v>
       </c>
       <c r="G14" t="n">
         <v>8.2736</v>
@@ -1546,13 +1546,13 @@
         <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5825</v>
+        <v>0.0314</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1219</v>
+        <v>0.1719</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4606</v>
+        <v>-0.1405</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.979</v>
+        <v>6.1452</v>
       </c>
       <c r="E15" t="n">
-        <v>7.8235</v>
+        <v>7.2359</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8445</v>
+        <v>-1.0908</v>
       </c>
       <c r="G15" t="n">
         <v>6.0034</v>
@@ -1624,13 +1624,13 @@
         <v>0.7411</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3642</v>
+        <v>0.5304</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1627</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2014</v>
+        <v>-0.0448</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9444</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7439</v>
+        <v>4.932</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9344</v>
+        <v>7.6343</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8095</v>
+        <v>-2.7023</v>
       </c>
       <c r="G16" t="n">
-        <v>5.0667</v>
+        <v>1.3078</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8914</v>
+        <v>0.9929</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1753</v>
+        <v>0.3149</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3234</v>
+        <v>4.9677</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2037</v>
+        <v>2.0955</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1197</v>
+        <v>2.8722</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2567</v>
+        <v>-3.6598</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6877</v>
+        <v>-1.1026</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9444</v>
+        <v>-2.5573</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7411</v>
+        <v>0.7411</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2234</v>
+        <v>-0.1853</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7327</v>
+        <v>0.3653</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8344</v>
+        <v>0.3342</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8983</v>
+        <v>0.0311</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3144</v>
+        <v>2.5177</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7848</v>
+        <v>4.4165</v>
       </c>
       <c r="E17" t="n">
-        <v>7.5364</v>
+        <v>3.5427</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.7516</v>
+        <v>0.8738</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3078</v>
+        <v>5.0667</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9929</v>
+        <v>4.8914</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3149</v>
+        <v>0.1753</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9677</v>
+        <v>5.3234</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0955</v>
+        <v>4.2037</v>
       </c>
       <c r="L17" t="n">
-        <v>2.8722</v>
+        <v>1.1197</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.6598</v>
+        <v>-0.2567</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1026</v>
+        <v>0.6877</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.5573</v>
+        <v>-0.9444</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7411</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1853</v>
+        <v>-2.2234</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9264</v>
+        <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2181</v>
+        <v>0.4054</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2363</v>
+        <v>0.4427</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0182</v>
+        <v>-0.0373</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5177</v>
+        <v>-0.3144</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4193</v>
+        <v>2.3471</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1125</v>
+        <v>3.8187</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6932</v>
+        <v>-1.4716</v>
       </c>
       <c r="G18" t="n">
         <v>1.7364</v>
@@ -1858,13 +1858,13 @@
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2228</v>
+        <v>-0.295</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6491</v>
+        <v>0.3554</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.872</v>
+        <v>-0.6504</v>
       </c>
       <c r="V18" t="n">
         <v>2.2027</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5021</v>
+        <v>1.1899</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7761</v>
+        <v>2.0698</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2739</v>
+        <v>-0.88</v>
       </c>
       <c r="G19" t="n">
         <v>2.0955</v>
@@ -1936,13 +1936,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2408</v>
+        <v>-0.5531</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2524</v>
+        <v>0.0414</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.5944</v>
       </c>
       <c r="V19" t="n">
         <v>0.9444</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.237</v>
+        <v>-0.1631</v>
       </c>
       <c r="E20" t="n">
         <v>-0.1023</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1346</v>
+        <v>-0.0608</v>
       </c>
       <c r="G20" t="n">
         <v>0.4747</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2119</v>
+        <v>-0.138</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2119</v>
+        <v>-0.138</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4831</v>
+        <v>-0.3846</v>
       </c>
       <c r="E21" t="n">
         <v>-0.8099</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3268</v>
+        <v>0.4253</v>
       </c>
       <c r="G21" t="n">
         <v>0.0829</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3808</v>
+        <v>-0.2823</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3261</v>
+        <v>-0.2276</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9139</v>
+        <v>-2.7678</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5788</v>
+        <v>-0.285</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3351</v>
+        <v>-2.4828</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9595</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0445</v>
+        <v>0.1906</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1977</v>
+        <v>0.0961</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2422</v>
+        <v>0.0945</v>
       </c>
       <c r="V22" t="n">
         <v>0.0011</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.223</v>
+        <v>-4.246</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2449</v>
+        <v>-1.5387</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9781</v>
+        <v>-2.7073</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2913</v>
@@ -2248,13 +2248,13 @@
         <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0047</v>
+        <v>-0.0277</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9103</v>
+        <v>0.6165</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.915</v>
+        <v>-0.6442</v>
       </c>
       <c r="V23" t="n">
         <v>1.2583</v>
@@ -2284,10 +2284,10 @@
         <v>27.6552</v>
       </c>
       <c r="E24" t="n">
-        <v>37.7688</v>
+        <v>37.7687</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.1135</v>
+        <v>-10.1137</v>
       </c>
       <c r="G24" t="n">
         <v>25.57210000000001</v>
@@ -2326,13 +2326,13 @@
         <v>7.4113</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1928000000000002</v>
+        <v>-0.1927000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>2.5307</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.7237</v>
+        <v>-2.7235</v>
       </c>
       <c r="V24" t="n">
         <v>5.9815</v>
